--- a/www/terminologies/ValueSet-JDV-J29-PublicPrisEnCharge-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J29-PublicPrisEnCharge-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="51" uniqueCount="49">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20250328120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2025-03-28T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -151,6 +151,12 @@
   </si>
   <si>
     <t>Personnes atteintes de pathologies chroniques ou présentant une affection de longue durée (ALD)</t>
+  </si>
+  <si>
+    <t>10</t>
+  </si>
+  <si>
+    <t>Victime de violence (intrafamiliale, professionnelle, prostitutionnelle, cyber)</t>
   </si>
   <si>
     <t/>
@@ -421,7 +427,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B12"/>
+  <dimension ref="A1:B13"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -513,15 +519,23 @@
         <v>46</v>
       </c>
       <c r="B11" t="s" s="2">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="12">
       <c r="A12" t="s" s="2">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
         <v>48</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="s" s="2">
+        <v>49</v>
+      </c>
+      <c r="B13" t="s" s="2">
+        <v>50</v>
       </c>
     </row>
   </sheetData>

--- a/www/terminologies/ValueSet-JDV-J29-PublicPrisEnCharge-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J29-PublicPrisEnCharge-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260330120000</t>
+    <t>20260629120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T12:00:00+01:00</t>
+    <t>2026-06-29T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -156,7 +156,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Victime de violence (intrafamiliale, professionnelle, prostitutionnelle, cyber)</t>
+    <t>Victime de violence</t>
   </si>
   <si>
     <t/>

--- a/www/terminologies/ValueSet-JDV-J29-PublicPrisEnCharge-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J29-PublicPrisEnCharge-ROR.xlsx
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260330120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-03-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -156,7 +156,7 @@
     <t>10</t>
   </si>
   <si>
-    <t>Victime de violence</t>
+    <t>Victime de violence (intrafamiliale, professionnelle, prostitutionnelle, cyber)</t>
   </si>
   <si>
     <t/>

--- a/www/terminologies/ValueSet-JDV-J29-PublicPrisEnCharge-ROR.xlsx
+++ b/www/terminologies/ValueSet-JDV-J29-PublicPrisEnCharge-ROR.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="53" uniqueCount="51">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="55" uniqueCount="53">
   <si>
     <t>Property</t>
   </si>
@@ -36,7 +36,7 @@
     <t>Version</t>
   </si>
   <si>
-    <t>20260629120000</t>
+    <t>20260730120000</t>
   </si>
   <si>
     <t>Name</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-29T12:00:00+01:00</t>
+    <t>2026-07-30T12:00:00+01:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -157,6 +157,12 @@
   </si>
   <si>
     <t>Victime de violence</t>
+  </si>
+  <si>
+    <t>11</t>
+  </si>
+  <si>
+    <t>Auteur de violence ou à risque de violence</t>
   </si>
   <si>
     <t/>
@@ -427,7 +433,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:B13"/>
+  <dimension ref="A1:B14"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="30.703125" customWidth="true"/>
@@ -527,15 +533,23 @@
         <v>48</v>
       </c>
       <c r="B12" t="s" s="2">
-        <v>48</v>
+        <v>49</v>
       </c>
     </row>
     <row r="13">
       <c r="A13" t="s" s="2">
-        <v>49</v>
+        <v>50</v>
       </c>
       <c r="B13" t="s" s="2">
         <v>50</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="s" s="2">
+        <v>51</v>
+      </c>
+      <c r="B14" t="s" s="2">
+        <v>52</v>
       </c>
     </row>
   </sheetData>
